--- a/artfynd/A 8660-2024 artfynd.xlsx
+++ b/artfynd/A 8660-2024 artfynd.xlsx
@@ -3585,10 +3585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117450538</v>
+        <v>117450527</v>
       </c>
       <c r="B27" t="n">
-        <v>56491</v>
+        <v>55891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,39 +3601,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>603246</v>
+        <v>603248</v>
       </c>
       <c r="R27" t="n">
-        <v>7027247</v>
+        <v>7027250</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3692,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117450527</v>
+        <v>117450538</v>
       </c>
       <c r="B28" t="n">
-        <v>55891</v>
+        <v>56492</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3708,34 +3703,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>603248</v>
+        <v>603246</v>
       </c>
       <c r="R28" t="n">
-        <v>7027250</v>
+        <v>7027247</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 8660-2024 artfynd.xlsx
+++ b/artfynd/A 8660-2024 artfynd.xlsx
@@ -6057,10 +6057,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119204985</v>
+        <v>119204940</v>
       </c>
       <c r="B51" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119204940</v>
+        <v>119204985</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>

--- a/artfynd/A 8660-2024 artfynd.xlsx
+++ b/artfynd/A 8660-2024 artfynd.xlsx
@@ -6060,7 +6060,7 @@
         <v>119204940</v>
       </c>
       <c r="B51" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>119204985</v>
       </c>
       <c r="B52" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 8660-2024 artfynd.xlsx
+++ b/artfynd/A 8660-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105166232</v>
+        <v>119238453</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
+        <v>90846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,17 +1180,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Sandåsberget, Sandåsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603321.871716036</v>
+        <v>603321</v>
       </c>
       <c r="R6" t="n">
-        <v>7027419.648361518</v>
+        <v>7027420</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,22 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,19 +1234,15 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5853,10 +5839,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119238453</v>
+        <v>119238163</v>
       </c>
       <c r="B49" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5869,21 +5855,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5893,13 +5879,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>603321</v>
+        <v>603318</v>
       </c>
       <c r="R49" t="n">
-        <v>7027420</v>
+        <v>7027464</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5955,10 +5941,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119238163</v>
+        <v>119204940</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5995,10 +5981,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>603318</v>
+        <v>603288</v>
       </c>
       <c r="R50" t="n">
-        <v>7027464</v>
+        <v>7027351</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6025,12 +6011,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6045,22 +6031,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119204940</v>
+        <v>119204985</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6073,21 +6059,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6159,10 +6145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119204985</v>
+        <v>120702229</v>
       </c>
       <c r="B52" t="n">
-        <v>90864</v>
+        <v>78594</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6175,21 +6161,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6199,13 +6185,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>603288</v>
+        <v>603226</v>
       </c>
       <c r="R52" t="n">
-        <v>7027351</v>
+        <v>7027434</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6229,12 +6215,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,22 +6235,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120702229</v>
+        <v>120702338</v>
       </c>
       <c r="B53" t="n">
-        <v>78594</v>
+        <v>98056</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6273,38 +6259,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sandåsberget, Sandåsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>603226</v>
+        <v>603252</v>
       </c>
       <c r="R53" t="n">
-        <v>7027434</v>
+        <v>7027430</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6363,10 +6353,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120702338</v>
+        <v>120702418</v>
       </c>
       <c r="B54" t="n">
-        <v>98056</v>
+        <v>91949</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6375,42 +6365,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sandåsberget, Sandåsberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>603252</v>
+        <v>603162</v>
       </c>
       <c r="R54" t="n">
-        <v>7027430</v>
+        <v>7027344</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6469,10 +6455,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120702418</v>
+        <v>120702226</v>
       </c>
       <c r="B55" t="n">
-        <v>91949</v>
+        <v>98056</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6481,38 +6467,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sandåsberget, Sandåsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>603162</v>
+        <v>603220</v>
       </c>
       <c r="R55" t="n">
-        <v>7027344</v>
+        <v>7027432</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6571,7 +6561,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120702226</v>
+        <v>120702259</v>
       </c>
       <c r="B56" t="n">
         <v>98056</v>
@@ -6606,7 +6596,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6615,10 +6605,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>603220</v>
+        <v>603259</v>
       </c>
       <c r="R56" t="n">
-        <v>7027432</v>
+        <v>7027428</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6674,112 +6664,6 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>120702259</v>
-      </c>
-      <c r="B57" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Sandåsberget, Sandåsberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>603259</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7027428</v>
-      </c>
-      <c r="S57" t="n">
-        <v>15</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
